--- a/03_test-cases/v1.0/fragments/TC-HUYDON-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-HUYDON-v1.0.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Huỷ đơn" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>

--- a/03_test-cases/v1.0/fragments/TC-HUYDON-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-HUYDON-v1.0.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$6:$U$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Huỷ đơn'!$A$6:$U$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage Matrix'!$A$1:$M$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="G9" s="239" t="inlineStr">
         <is>
-          <t>Đơn đang ở trạng thái "Đã ghép", Carrier chưa bấm "Tôi đã lấy hàng"</t>
+          <t>Đơn đang ở trạng thái "Đã ghép" (chưa chuyển "Đang giao"); user đăng nhập là Sender, Carrier, hoặc Receiver của đơn</t>
         </is>
       </c>
       <c r="H9" s="239" t="inlineStr">
         <is>
-          <t>1. Mở app FoxEco bằng tài khoản Người vận chuyển (Carrier)
+          <t>1. Mở app FoxEco bằng tài khoản Sender/Carrier/Receiver
 2. Bấm tab "Hoạt động", mở đơn đang nhận (trạng thái "Đã ghép") để vào màn "Theo dõi đơn"
 3. Bấm "✕ Huỷ nhận đơn" và quan sát popup vừa hiện</t>
         </is>
@@ -5244,159 +5244,150 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1" s="206">
-      <c r="A35" s="231" t="n"/>
-      <c r="B35" s="232" t="inlineStr">
+    <row r="35" ht="60" customHeight="1" s="206">
+      <c r="A35" s="239">
+        <f>IF(C35="","",$C$2&amp;"."&amp;COUNTA($C$8:C35)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B35" s="239" t="inlineStr">
+        <is>
+          <t>REQ-CNL-001</t>
+        </is>
+      </c>
+      <c r="C35" s="239" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-01 §D3/§D4/§A5/§D1b (CNL-01, BR-CNL-01, BR-INT-05, US-D16)</t>
+        </is>
+      </c>
+      <c r="D35" s="239" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E35" s="239" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F35" s="239" t="inlineStr">
+        <is>
+          <t>Check LỊCH SỬ ghi log khi Người nhận huỷ đơn</t>
+        </is>
+      </c>
+      <c r="G35" s="239" t="inlineStr">
+        <is>
+          <t>Đơn đang ở trạng thái "Đã ghép", user đăng nhập là Receiver của đơn</t>
+        </is>
+      </c>
+      <c r="H35" s="239" t="inlineStr">
+        <is>
+          <t>1. Mở app FoxEco bằng tài khoản Người nhận (Receiver)
+2. Bấm tab "Hoạt động", mở đơn cần huỷ để vào màn "Theo dõi đơn"
+3. Bấm "Huỷ đơn", nhập lý do "Không ở văn phòng", bấm "Xác nhận", rồi cuộn xuống khối "LỊCH SỬ"</t>
+        </is>
+      </c>
+      <c r="I35" s="239" t="inlineStr">
+        <is>
+          <t>3. Khối "LỊCH SỬ" ghi thêm 1 mốc cho hành động huỷ (vai trò người huỷ + lý do + timestamp), nối tiếp đúng thứ tự sau các mốc trước đó — KHÔNG chỉ hiện banner đỏ "Đơn hàng đã bị huỷ" rồi bỏ trống LỊCH SỬ</t>
+        </is>
+      </c>
+      <c r="J35" s="239" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K35" s="239" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L35" s="239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M35" s="239" t="n"/>
+      <c r="N35" s="239" t="n"/>
+      <c r="O35" s="239" t="n"/>
+      <c r="P35" s="239" t="n"/>
+      <c r="Q35" s="239" t="n"/>
+      <c r="R35" s="239" t="n"/>
+      <c r="S35" s="239" t="n"/>
+      <c r="T35" s="239" t="n"/>
+      <c r="U35" s="239" t="n"/>
+      <c r="V35" s="239" t="n"/>
+      <c r="W35" s="239" t="n"/>
+      <c r="X35" s="239" t="n"/>
+      <c r="Y35" s="239" t="n"/>
+      <c r="Z35" s="239" t="n"/>
+      <c r="AA35" s="239" t="n"/>
+      <c r="AB35" s="240" t="n"/>
+      <c r="AC35" s="240" t="n"/>
+      <c r="AD35" s="240" t="n"/>
+      <c r="AE35" s="240" t="n"/>
+      <c r="AF35" s="240" t="n"/>
+      <c r="AG35" s="240" t="n"/>
+      <c r="AH35" s="240" t="n"/>
+      <c r="AI35" s="240" t="n"/>
+      <c r="AJ35" s="240" t="n"/>
+      <c r="AK35" s="240" t="n"/>
+      <c r="AL35" s="240" t="n"/>
+      <c r="AM35" s="241" t="n"/>
+      <c r="AN35" s="241" t="n"/>
+      <c r="AO35" s="241" t="n"/>
+      <c r="AP35" s="240" t="inlineStr">
+        <is>
+          <t>Nguồn: merge CA v1.1 `C-CANCEL-2` — user chốt "huy don va huy nhan don hien tai cu luu log lich su nha". ⚠ CA đã live-verify qua Chrome MCP (2026-07-29): UI hiện tại KHÔNG ghi log nào vào LỊCH SỬ khi huỷ → TC này DỰ KIẾN FAIL, là gap cần dev bổ sung (không phải lỗi TC). Bổ sung 2026-07-30 theo yêu cầu user để đủ 3/3 vai trò cho phần LỊCH SỬ (trước đó chỉ có Sender `TC_08.22` + Carrier `TC_08.23`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" s="206">
+      <c r="A36" s="231" t="n"/>
+      <c r="B36" s="232" t="inlineStr">
         <is>
           <t>Block Carrier huỷ nhận đơn → trả lại "Chờ ghép"</t>
         </is>
       </c>
-      <c r="C35" s="211" t="n"/>
-      <c r="D35" s="211" t="n"/>
-      <c r="E35" s="211" t="n"/>
-      <c r="F35" s="211" t="n"/>
-      <c r="G35" s="211" t="n"/>
-      <c r="H35" s="211" t="n"/>
-      <c r="I35" s="209" t="n"/>
-      <c r="J35" s="231" t="n"/>
-      <c r="K35" s="231" t="n"/>
-      <c r="L35" s="231" t="n"/>
-      <c r="M35" s="231" t="n"/>
-      <c r="N35" s="235" t="n"/>
-      <c r="O35" s="235" t="n"/>
-      <c r="P35" s="235" t="n"/>
-      <c r="Q35" s="235" t="n"/>
-      <c r="R35" s="235" t="n"/>
-      <c r="S35" s="235" t="n"/>
-      <c r="T35" s="235" t="n"/>
-      <c r="U35" s="235" t="n"/>
-      <c r="V35" s="235" t="n"/>
-      <c r="W35" s="235" t="n"/>
-      <c r="X35" s="235" t="n"/>
-      <c r="Y35" s="235" t="n"/>
-      <c r="Z35" s="235" t="n"/>
-      <c r="AA35" s="235" t="n"/>
-      <c r="AB35" s="236" t="n"/>
-      <c r="AC35" s="236" t="n"/>
-      <c r="AD35" s="236" t="n"/>
-      <c r="AE35" s="236" t="n"/>
-      <c r="AF35" s="236" t="n"/>
-      <c r="AG35" s="236" t="n"/>
-      <c r="AH35" s="236" t="n"/>
-      <c r="AI35" s="236" t="n"/>
-      <c r="AJ35" s="236" t="n"/>
-      <c r="AK35" s="236" t="n"/>
-      <c r="AL35" s="236" t="n"/>
-      <c r="AM35" s="237" t="n"/>
-      <c r="AN35" s="237" t="n"/>
-      <c r="AO35" s="237" t="n"/>
-      <c r="AP35" s="238" t="n"/>
-    </row>
-    <row r="36" ht="60" customHeight="1" s="206">
-      <c r="A36" s="239">
-        <f>IF(C36="","",$C$2&amp;"."&amp;COUNTA($C$8:C36)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="B36" s="239" t="inlineStr">
-        <is>
-          <t>REQ-CNL-002</t>
-        </is>
-      </c>
-      <c r="C36" s="239" t="inlineStr">
-        <is>
-          <t>DOC-v1.0-01 §D7 (OPR-09)</t>
-        </is>
-      </c>
-      <c r="D36" s="239" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E36" s="239" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F36" s="239" t="inlineStr">
-        <is>
-          <t>Check Carrier huỷ nhận đơn khi chưa lấy hàng → đơn tự động về "Chờ ghép"</t>
-        </is>
-      </c>
-      <c r="G36" s="239" t="inlineStr">
-        <is>
-          <t>Đơn đang ở trạng thái "Đã ghép", Carrier CHƯA bấm "Tôi đã lấy hàng"</t>
-        </is>
-      </c>
-      <c r="H36" s="239" t="inlineStr">
-        <is>
-          <t>1. Mở app FoxEco bằng tài khoản Người vận chuyển (Carrier)
-2. Bấm tab "Hoạt động", mở đơn đang nhận (trạng thái "Đã ghép") để vào màn "Theo dõi đơn"
-3. Bấm "✕ Huỷ nhận đơn" để mở popup, nhập lý do "Đổi lịch công tác" rồi bấm "Xác nhận"</t>
-        </is>
-      </c>
-      <c r="I36" s="239" t="inlineStr">
-        <is>
-          <t>3. Đơn tự động quay về trạng thái "Chờ ghép" (POSTED) — KHÔNG chuyển sang trạng thái đã huỷ như trường hợp Sender/Receiver huỷ</t>
-        </is>
-      </c>
-      <c r="J36" s="239" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="K36" s="239" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L36" s="239" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M36" s="239" t="n"/>
-      <c r="N36" s="239" t="n"/>
-      <c r="O36" s="239" t="n"/>
-      <c r="P36" s="239" t="n"/>
-      <c r="Q36" s="239" t="n"/>
-      <c r="R36" s="239" t="n"/>
-      <c r="S36" s="239" t="n"/>
-      <c r="T36" s="239" t="n"/>
-      <c r="U36" s="239" t="n"/>
-      <c r="V36" s="239" t="n"/>
-      <c r="W36" s="239" t="n"/>
-      <c r="X36" s="239" t="n"/>
-      <c r="Y36" s="239" t="n"/>
-      <c r="Z36" s="239" t="n"/>
-      <c r="AA36" s="239" t="n"/>
-      <c r="AB36" s="240" t="n"/>
-      <c r="AC36" s="240" t="n"/>
-      <c r="AD36" s="240" t="n"/>
-      <c r="AE36" s="240" t="n"/>
-      <c r="AF36" s="240" t="n"/>
-      <c r="AG36" s="240" t="n"/>
-      <c r="AH36" s="240" t="n"/>
-      <c r="AI36" s="240" t="n"/>
-      <c r="AJ36" s="240" t="n"/>
-      <c r="AK36" s="240" t="n"/>
-      <c r="AL36" s="240" t="n"/>
-      <c r="AM36" s="241">
-        <f>IF($A36="","",IF(OR($N36="Yes",$S36="Yes",$X36="Yes",$AC36="Yes",$AH36="Yes"),"Yes","No"))</f>
-        <v/>
-      </c>
-      <c r="AN36" s="241">
-        <f>IF($A36="","",IFERROR(IF($AI36&lt;&gt;"",$AI36,IF($AD36&lt;&gt;"",$AD36,IF($Y36&lt;&gt;"",$Y36,IF($T36&lt;&gt;"",$T36,IF($O36&lt;&gt;"",$O36,""))))),""))</f>
-        <v/>
-      </c>
-      <c r="AO36" s="241">
-        <f>IFERROR(IF($AJ36&lt;&gt;"",$AJ36,IF($AE36&lt;&gt;"",$AE36,IF($Z36&lt;&gt;"",$Z36,IF($U36&lt;&gt;"",$U36,IF($P36&lt;&gt;"",$P36,""))))),"")</f>
-        <v/>
-      </c>
-      <c r="AP36" s="240" t="inlineStr">
-        <is>
-          <t>Technique: ST-matched-posted (huỷ nhận trước khi lấy hàng) | Bề mặt Bảng tin của cùng hành vi (tin hiện lại + được khớp lại) đã cover tại TC-BANGTIN (SC-ASN-012) — không lặp</t>
-        </is>
-      </c>
+      <c r="C36" s="211" t="n"/>
+      <c r="D36" s="211" t="n"/>
+      <c r="E36" s="211" t="n"/>
+      <c r="F36" s="211" t="n"/>
+      <c r="G36" s="211" t="n"/>
+      <c r="H36" s="211" t="n"/>
+      <c r="I36" s="209" t="n"/>
+      <c r="J36" s="231" t="n"/>
+      <c r="K36" s="231" t="n"/>
+      <c r="L36" s="231" t="n"/>
+      <c r="M36" s="231" t="n"/>
+      <c r="N36" s="235" t="n"/>
+      <c r="O36" s="235" t="n"/>
+      <c r="P36" s="235" t="n"/>
+      <c r="Q36" s="235" t="n"/>
+      <c r="R36" s="235" t="n"/>
+      <c r="S36" s="235" t="n"/>
+      <c r="T36" s="235" t="n"/>
+      <c r="U36" s="235" t="n"/>
+      <c r="V36" s="235" t="n"/>
+      <c r="W36" s="235" t="n"/>
+      <c r="X36" s="235" t="n"/>
+      <c r="Y36" s="235" t="n"/>
+      <c r="Z36" s="235" t="n"/>
+      <c r="AA36" s="235" t="n"/>
+      <c r="AB36" s="236" t="n"/>
+      <c r="AC36" s="236" t="n"/>
+      <c r="AD36" s="236" t="n"/>
+      <c r="AE36" s="236" t="n"/>
+      <c r="AF36" s="236" t="n"/>
+      <c r="AG36" s="236" t="n"/>
+      <c r="AH36" s="236" t="n"/>
+      <c r="AI36" s="236" t="n"/>
+      <c r="AJ36" s="236" t="n"/>
+      <c r="AK36" s="236" t="n"/>
+      <c r="AL36" s="236" t="n"/>
+      <c r="AM36" s="237" t="n"/>
+      <c r="AN36" s="237" t="n"/>
+      <c r="AO36" s="237" t="n"/>
+      <c r="AP36" s="238" t="n"/>
     </row>
     <row r="37" ht="60" customHeight="1" s="206">
       <c r="A37" s="239">
@@ -5420,29 +5411,29 @@
       </c>
       <c r="E37" s="239" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F37" s="239" t="inlineStr">
         <is>
-          <t>Check Người gửi và Người nhận thấy đơn quay về "Chờ ghép" ngay sau khi Carrier huỷ nhận</t>
+          <t>Check Carrier huỷ nhận đơn khi chưa lấy hàng → đơn tự động về "Chờ ghép"</t>
         </is>
       </c>
       <c r="G37" s="239" t="inlineStr">
         <is>
-          <t>Đơn đang ở "Đã ghép"; 3 tài khoản Sender / Carrier / Receiver đang mở sẵn màn Theo dõi đơn</t>
+          <t>Đơn đang ở trạng thái "Đã ghép", Carrier CHƯA bấm "Tôi đã lấy hàng"</t>
         </is>
       </c>
       <c r="H37" s="239" t="inlineStr">
         <is>
-          <t>1. Trên thiết bị Carrier: bấm "✕ Huỷ nhận đơn", nhập lý do "Đổi lịch công tác" rồi bấm "Xác nhận"
-2. Ngay sau đó quan sát màn Theo dõi đơn trên thiết bị Sender
-3. Ngay sau đó quan sát màn Theo dõi đơn trên thiết bị Receiver</t>
+          <t>1. Mở app FoxEco bằng tài khoản Người vận chuyển (Carrier)
+2. Bấm tab "Hoạt động", mở đơn đang nhận (trạng thái "Đã ghép") để vào màn "Theo dõi đơn"
+3. Bấm "✕ Huỷ nhận đơn" để mở popup, nhập lý do "Đổi lịch công tác" rồi bấm "Xác nhận"</t>
         </is>
       </c>
       <c r="I37" s="239" t="inlineStr">
         <is>
-          <t>3. Màn Sender và Receiver đều tự chuyển về trạng thái "Chờ ghép", khối "Liên hệ Người vận chuyển"/"Người giao hàng" biến mất — không cần tải lại thủ công</t>
+          <t>3. Đơn tự động quay về trạng thái "Chờ ghép" (POSTED) — KHÔNG chuyển sang trạng thái đã huỷ như trường hợp Sender/Receiver huỷ</t>
         </is>
       </c>
       <c r="J37" s="239" t="inlineStr">
@@ -5487,172 +5478,172 @@
       <c r="AK37" s="240" t="n"/>
       <c r="AL37" s="240" t="n"/>
       <c r="AM37" s="241">
+        <f>IF($A36="","",IF(OR($N36="Yes",$S36="Yes",$X36="Yes",$AC36="Yes",$AH36="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN37" s="241">
+        <f>IF($A36="","",IFERROR(IF($AI36&lt;&gt;"",$AI36,IF($AD36&lt;&gt;"",$AD36,IF($Y36&lt;&gt;"",$Y36,IF($T36&lt;&gt;"",$T36,IF($O36&lt;&gt;"",$O36,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO37" s="241">
+        <f>IFERROR(IF($AJ36&lt;&gt;"",$AJ36,IF($AE36&lt;&gt;"",$AE36,IF($Z36&lt;&gt;"",$Z36,IF($U36&lt;&gt;"",$U36,IF($P36&lt;&gt;"",$P36,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP37" s="240" t="inlineStr">
+        <is>
+          <t>Technique: ST-matched-posted (huỷ nhận trước khi lấy hàng) | Bề mặt Bảng tin của cùng hành vi (tin hiện lại + được khớp lại) đã cover tại TC-BANGTIN (SC-ASN-012) — không lặp</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1" s="206">
+      <c r="A38" s="239">
+        <f>IF(C38="","",$C$2&amp;"."&amp;COUNTA($C$8:C38)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B38" s="239" t="inlineStr">
+        <is>
+          <t>REQ-CNL-002</t>
+        </is>
+      </c>
+      <c r="C38" s="239" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-01 §D7 (OPR-09)</t>
+        </is>
+      </c>
+      <c r="D38" s="239" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E38" s="239" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F38" s="239" t="inlineStr">
+        <is>
+          <t>Check Người gửi và Người nhận thấy đơn quay về "Chờ ghép" ngay sau khi Carrier huỷ nhận</t>
+        </is>
+      </c>
+      <c r="G38" s="239" t="inlineStr">
+        <is>
+          <t>Đơn đang ở "Đã ghép"; 3 tài khoản Sender / Carrier / Receiver đang mở sẵn màn Theo dõi đơn</t>
+        </is>
+      </c>
+      <c r="H38" s="239" t="inlineStr">
+        <is>
+          <t>1. Trên thiết bị Carrier: bấm "✕ Huỷ nhận đơn", nhập lý do "Đổi lịch công tác" rồi bấm "Xác nhận"
+2. Ngay sau đó quan sát màn Theo dõi đơn trên thiết bị Sender
+3. Ngay sau đó quan sát màn Theo dõi đơn trên thiết bị Receiver</t>
+        </is>
+      </c>
+      <c r="I38" s="239" t="inlineStr">
+        <is>
+          <t>3. Màn Sender và Receiver đều tự chuyển về trạng thái "Chờ ghép", khối "Liên hệ Người vận chuyển"/"Người giao hàng" biến mất — không cần tải lại thủ công</t>
+        </is>
+      </c>
+      <c r="J38" s="239" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K38" s="239" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L38" s="239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M38" s="239" t="n"/>
+      <c r="N38" s="239" t="n"/>
+      <c r="O38" s="239" t="n"/>
+      <c r="P38" s="239" t="n"/>
+      <c r="Q38" s="239" t="n"/>
+      <c r="R38" s="239" t="n"/>
+      <c r="S38" s="239" t="n"/>
+      <c r="T38" s="239" t="n"/>
+      <c r="U38" s="239" t="n"/>
+      <c r="V38" s="239" t="n"/>
+      <c r="W38" s="239" t="n"/>
+      <c r="X38" s="239" t="n"/>
+      <c r="Y38" s="239" t="n"/>
+      <c r="Z38" s="239" t="n"/>
+      <c r="AA38" s="239" t="n"/>
+      <c r="AB38" s="240" t="n"/>
+      <c r="AC38" s="240" t="n"/>
+      <c r="AD38" s="240" t="n"/>
+      <c r="AE38" s="240" t="n"/>
+      <c r="AF38" s="240" t="n"/>
+      <c r="AG38" s="240" t="n"/>
+      <c r="AH38" s="240" t="n"/>
+      <c r="AI38" s="240" t="n"/>
+      <c r="AJ38" s="240" t="n"/>
+      <c r="AK38" s="240" t="n"/>
+      <c r="AL38" s="240" t="n"/>
+      <c r="AM38" s="241">
         <f>IF($A37="","",IF(OR($N37="Yes",$S37="Yes",$X37="Yes",$AC37="Yes",$AH37="Yes"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="AN37" s="241">
+      <c r="AN38" s="241">
         <f>IF($A37="","",IFERROR(IF($AI37&lt;&gt;"",$AI37,IF($AD37&lt;&gt;"",$AD37,IF($Y37&lt;&gt;"",$Y37,IF($T37&lt;&gt;"",$T37,IF($O37&lt;&gt;"",$O37,""))))),""))</f>
         <v/>
       </c>
-      <c r="AO37" s="241">
+      <c r="AO38" s="241">
         <f>IFERROR(IF($AJ37&lt;&gt;"",$AJ37,IF($AE37&lt;&gt;"",$AE37,IF($Z37&lt;&gt;"",$Z37,IF($U37&lt;&gt;"",$U37,IF($P37&lt;&gt;"",$P37,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP37" s="240" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1" s="206">
-      <c r="A38" s="231" t="n"/>
-      <c r="B38" s="232" t="inlineStr">
+      <c r="AP38" s="240" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1" s="206">
+      <c r="A39" s="231" t="n"/>
+      <c r="B39" s="232" t="inlineStr">
         <is>
           <t>Block Chặn huỷ thường sau khi đã lấy hàng (OPR-11)</t>
         </is>
       </c>
-      <c r="C38" s="211" t="n"/>
-      <c r="D38" s="211" t="n"/>
-      <c r="E38" s="211" t="n"/>
-      <c r="F38" s="211" t="n"/>
-      <c r="G38" s="211" t="n"/>
-      <c r="H38" s="211" t="n"/>
-      <c r="I38" s="209" t="n"/>
-      <c r="J38" s="231" t="n"/>
-      <c r="K38" s="231" t="n"/>
-      <c r="L38" s="231" t="n"/>
-      <c r="M38" s="231" t="n"/>
-      <c r="N38" s="235" t="n"/>
-      <c r="O38" s="235" t="n"/>
-      <c r="P38" s="235" t="n"/>
-      <c r="Q38" s="235" t="n"/>
-      <c r="R38" s="235" t="n"/>
-      <c r="S38" s="235" t="n"/>
-      <c r="T38" s="235" t="n"/>
-      <c r="U38" s="235" t="n"/>
-      <c r="V38" s="235" t="n"/>
-      <c r="W38" s="235" t="n"/>
-      <c r="X38" s="235" t="n"/>
-      <c r="Y38" s="235" t="n"/>
-      <c r="Z38" s="235" t="n"/>
-      <c r="AA38" s="235" t="n"/>
-      <c r="AB38" s="236" t="n"/>
-      <c r="AC38" s="236" t="n"/>
-      <c r="AD38" s="236" t="n"/>
-      <c r="AE38" s="236" t="n"/>
-      <c r="AF38" s="236" t="n"/>
-      <c r="AG38" s="236" t="n"/>
-      <c r="AH38" s="236" t="n"/>
-      <c r="AI38" s="236" t="n"/>
-      <c r="AJ38" s="236" t="n"/>
-      <c r="AK38" s="236" t="n"/>
-      <c r="AL38" s="236" t="n"/>
-      <c r="AM38" s="237" t="n"/>
-      <c r="AN38" s="237" t="n"/>
-      <c r="AO38" s="237" t="n"/>
-      <c r="AP38" s="238" t="n"/>
-    </row>
-    <row r="39" ht="60" customHeight="1" s="206">
-      <c r="A39" s="239">
-        <f>IF(C39="","",$C$2&amp;"."&amp;COUNTA($C$8:C39)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="B39" s="239" t="inlineStr">
-        <is>
-          <t>REQ-CNL-003</t>
-        </is>
-      </c>
-      <c r="C39" s="239" t="inlineStr">
-        <is>
-          <t>DOC-v1.0-01 §D7 (OPR-11)</t>
-        </is>
-      </c>
-      <c r="D39" s="239" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E39" s="239" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F39" s="239" t="inlineStr">
-        <is>
-          <t>Check Người nhận KHÔNG còn nút "Huỷ đơn" khi đơn đã "Đang giao"</t>
-        </is>
-      </c>
-      <c r="G39" s="239" t="inlineStr">
-        <is>
-          <t>Đơn đã chuyển sang "Đang giao" (Carrier đã bấm "Tôi đã lấy hàng"), user đăng nhập là Receiver</t>
-        </is>
-      </c>
-      <c r="H39" s="239" t="inlineStr">
-        <is>
-          <t>1. Mở app FoxEco bằng tài khoản Người nhận (Receiver)
-2. Bấm tab "Hoạt động", mở đơn cần huỷ để vào màn "Theo dõi đơn"
-3. Tìm nút "Huỷ đơn" trên màn Theo dõi đơn</t>
-        </is>
-      </c>
-      <c r="I39" s="239" t="inlineStr">
-        <is>
-          <t>3. Nút "Huỷ đơn" KHÔNG còn hiển thị (hoặc disable) — Receiver không huỷ được đơn sau khi hàng đã được lấy</t>
-        </is>
-      </c>
-      <c r="J39" s="239" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="K39" s="239" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L39" s="239" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M39" s="239" t="n"/>
-      <c r="N39" s="239" t="n"/>
-      <c r="O39" s="239" t="n"/>
-      <c r="P39" s="239" t="n"/>
-      <c r="Q39" s="239" t="n"/>
-      <c r="R39" s="239" t="n"/>
-      <c r="S39" s="239" t="n"/>
-      <c r="T39" s="239" t="n"/>
-      <c r="U39" s="239" t="n"/>
-      <c r="V39" s="239" t="n"/>
-      <c r="W39" s="239" t="n"/>
-      <c r="X39" s="239" t="n"/>
-      <c r="Y39" s="239" t="n"/>
-      <c r="Z39" s="239" t="n"/>
-      <c r="AA39" s="239" t="n"/>
-      <c r="AB39" s="240" t="n"/>
-      <c r="AC39" s="240" t="n"/>
-      <c r="AD39" s="240" t="n"/>
-      <c r="AE39" s="240" t="n"/>
-      <c r="AF39" s="240" t="n"/>
-      <c r="AG39" s="240" t="n"/>
-      <c r="AH39" s="240" t="n"/>
-      <c r="AI39" s="240" t="n"/>
-      <c r="AJ39" s="240" t="n"/>
-      <c r="AK39" s="240" t="n"/>
-      <c r="AL39" s="240" t="n"/>
-      <c r="AM39" s="241">
-        <f>IF($A39="","",IF(OR($N39="Yes",$S39="Yes",$X39="Yes",$AC39="Yes",$AH39="Yes"),"Yes","No"))</f>
-        <v/>
-      </c>
-      <c r="AN39" s="241">
-        <f>IF($A39="","",IFERROR(IF($AI39&lt;&gt;"",$AI39,IF($AD39&lt;&gt;"",$AD39,IF($Y39&lt;&gt;"",$Y39,IF($T39&lt;&gt;"",$T39,IF($O39&lt;&gt;"",$O39,""))))),""))</f>
-        <v/>
-      </c>
-      <c r="AO39" s="241">
-        <f>IFERROR(IF($AJ39&lt;&gt;"",$AJ39,IF($AE39&lt;&gt;"",$AE39,IF($Z39&lt;&gt;"",$Z39,IF($U39&lt;&gt;"",$U39,IF($P39&lt;&gt;"",$P39,""))))),"")</f>
-        <v/>
-      </c>
-      <c r="AP39" s="240" t="inlineStr">
-        <is>
-          <t>Technique: EP-receiver-blocked | Nhánh Sender/Carrier ở cùng trạng thái "Đang giao" đã cover tại TC-THEODOIDON (SC-DLV-009) — không lặp</t>
-        </is>
-      </c>
+      <c r="C39" s="211" t="n"/>
+      <c r="D39" s="211" t="n"/>
+      <c r="E39" s="211" t="n"/>
+      <c r="F39" s="211" t="n"/>
+      <c r="G39" s="211" t="n"/>
+      <c r="H39" s="211" t="n"/>
+      <c r="I39" s="209" t="n"/>
+      <c r="J39" s="231" t="n"/>
+      <c r="K39" s="231" t="n"/>
+      <c r="L39" s="231" t="n"/>
+      <c r="M39" s="231" t="n"/>
+      <c r="N39" s="235" t="n"/>
+      <c r="O39" s="235" t="n"/>
+      <c r="P39" s="235" t="n"/>
+      <c r="Q39" s="235" t="n"/>
+      <c r="R39" s="235" t="n"/>
+      <c r="S39" s="235" t="n"/>
+      <c r="T39" s="235" t="n"/>
+      <c r="U39" s="235" t="n"/>
+      <c r="V39" s="235" t="n"/>
+      <c r="W39" s="235" t="n"/>
+      <c r="X39" s="235" t="n"/>
+      <c r="Y39" s="235" t="n"/>
+      <c r="Z39" s="235" t="n"/>
+      <c r="AA39" s="235" t="n"/>
+      <c r="AB39" s="236" t="n"/>
+      <c r="AC39" s="236" t="n"/>
+      <c r="AD39" s="236" t="n"/>
+      <c r="AE39" s="236" t="n"/>
+      <c r="AF39" s="236" t="n"/>
+      <c r="AG39" s="236" t="n"/>
+      <c r="AH39" s="236" t="n"/>
+      <c r="AI39" s="236" t="n"/>
+      <c r="AJ39" s="236" t="n"/>
+      <c r="AK39" s="236" t="n"/>
+      <c r="AL39" s="236" t="n"/>
+      <c r="AM39" s="237" t="n"/>
+      <c r="AN39" s="237" t="n"/>
+      <c r="AO39" s="237" t="n"/>
+      <c r="AP39" s="238" t="n"/>
     </row>
     <row r="40" ht="60" customHeight="1" s="206">
       <c r="A40" s="239">
@@ -5681,24 +5672,24 @@
       </c>
       <c r="F40" s="239" t="inlineStr">
         <is>
-          <t>Check cả 3 vai trò đều KHÔNG huỷ được đơn khi đơn đã "Đã giao"</t>
+          <t>Check Người nhận KHÔNG còn nút "Huỷ đơn" khi đơn đã "Đang giao"</t>
         </is>
       </c>
       <c r="G40" s="239" t="inlineStr">
         <is>
-          <t>Đơn đang ở trạng thái "Đã giao" (DELIVERED); có sẵn cả 3 tài khoản Sender / Carrier / Receiver của đơn</t>
+          <t>Đơn đã chuyển sang "Đang giao" (Carrier đã bấm "Tôi đã lấy hàng"), user đăng nhập là Receiver</t>
         </is>
       </c>
       <c r="H40" s="239" t="inlineStr">
         <is>
-          <t>1. Mở app FoxEco lần lượt bằng cả 3 tài khoản Sender, Carrier, Receiver của cùng đơn
-2. Với mỗi tài khoản, mở màn Theo dõi đơn của đơn đó
-3. Tìm nút "Huỷ đơn"/"Huỷ nhận đơn" trên màn của từng vai trò</t>
+          <t>1. Mở app FoxEco bằng tài khoản Người nhận (Receiver)
+2. Bấm tab "Hoạt động", mở đơn cần huỷ để vào màn "Theo dõi đơn"
+3. Tìm nút "Huỷ đơn" trên màn Theo dõi đơn</t>
         </is>
       </c>
       <c r="I40" s="239" t="inlineStr">
         <is>
-          <t>3. Không vai trò nào còn nút huỷ khả dụng — đường huỷ thường bị khoá hoàn toàn từ mốc đã lấy hàng trở đi (OPR-11)</t>
+          <t>3. Nút "Huỷ đơn" KHÔNG còn hiển thị (hoặc disable) — Receiver không huỷ được đơn sau khi hàng đã được lấy</t>
         </is>
       </c>
       <c r="J40" s="239" t="inlineStr">
@@ -5743,66 +5734,128 @@
       <c r="AK40" s="240" t="n"/>
       <c r="AL40" s="240" t="n"/>
       <c r="AM40" s="241">
+        <f>IF($A39="","",IF(OR($N39="Yes",$S39="Yes",$X39="Yes",$AC39="Yes",$AH39="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN40" s="241">
+        <f>IF($A39="","",IFERROR(IF($AI39&lt;&gt;"",$AI39,IF($AD39&lt;&gt;"",$AD39,IF($Y39&lt;&gt;"",$Y39,IF($T39&lt;&gt;"",$T39,IF($O39&lt;&gt;"",$O39,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO40" s="241">
+        <f>IFERROR(IF($AJ39&lt;&gt;"",$AJ39,IF($AE39&lt;&gt;"",$AE39,IF($Z39&lt;&gt;"",$Z39,IF($U39&lt;&gt;"",$U39,IF($P39&lt;&gt;"",$P39,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP40" s="240" t="inlineStr">
+        <is>
+          <t>Technique: EP-receiver-blocked | Nhánh Sender/Carrier ở cùng trạng thái "Đang giao" đã cover tại TC-THEODOIDON (SC-DLV-009) — không lặp</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1" s="206">
+      <c r="A41" s="239">
+        <f>IF(C41="","",$C$2&amp;"."&amp;COUNTA($C$8:C41)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B41" s="239" t="inlineStr">
+        <is>
+          <t>REQ-CNL-003</t>
+        </is>
+      </c>
+      <c r="C41" s="239" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-01 §D7 (OPR-11)</t>
+        </is>
+      </c>
+      <c r="D41" s="239" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E41" s="239" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F41" s="239" t="inlineStr">
+        <is>
+          <t>Check cả 3 vai trò đều KHÔNG huỷ được đơn khi đơn đã "Đã giao"</t>
+        </is>
+      </c>
+      <c r="G41" s="239" t="inlineStr">
+        <is>
+          <t>Đơn đang ở trạng thái "Đã giao" (DELIVERED); có sẵn cả 3 tài khoản Sender / Carrier / Receiver của đơn</t>
+        </is>
+      </c>
+      <c r="H41" s="239" t="inlineStr">
+        <is>
+          <t>1. Mở app FoxEco lần lượt bằng cả 3 tài khoản Sender, Carrier, Receiver của cùng đơn
+2. Với mỗi tài khoản, mở màn Theo dõi đơn của đơn đó
+3. Tìm nút "Huỷ đơn"/"Huỷ nhận đơn" trên màn của từng vai trò</t>
+        </is>
+      </c>
+      <c r="I41" s="239" t="inlineStr">
+        <is>
+          <t>3. Không vai trò nào còn nút huỷ khả dụng — đường huỷ thường bị khoá hoàn toàn từ mốc đã lấy hàng trở đi (OPR-11)</t>
+        </is>
+      </c>
+      <c r="J41" s="239" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K41" s="239" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L41" s="239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M41" s="239" t="n"/>
+      <c r="N41" s="239" t="n"/>
+      <c r="O41" s="239" t="n"/>
+      <c r="P41" s="239" t="n"/>
+      <c r="Q41" s="239" t="n"/>
+      <c r="R41" s="239" t="n"/>
+      <c r="S41" s="239" t="n"/>
+      <c r="T41" s="239" t="n"/>
+      <c r="U41" s="239" t="n"/>
+      <c r="V41" s="239" t="n"/>
+      <c r="W41" s="239" t="n"/>
+      <c r="X41" s="239" t="n"/>
+      <c r="Y41" s="239" t="n"/>
+      <c r="Z41" s="239" t="n"/>
+      <c r="AA41" s="239" t="n"/>
+      <c r="AB41" s="240" t="n"/>
+      <c r="AC41" s="240" t="n"/>
+      <c r="AD41" s="240" t="n"/>
+      <c r="AE41" s="240" t="n"/>
+      <c r="AF41" s="240" t="n"/>
+      <c r="AG41" s="240" t="n"/>
+      <c r="AH41" s="240" t="n"/>
+      <c r="AI41" s="240" t="n"/>
+      <c r="AJ41" s="240" t="n"/>
+      <c r="AK41" s="240" t="n"/>
+      <c r="AL41" s="240" t="n"/>
+      <c r="AM41" s="241">
         <f>IF($A40="","",IF(OR($N40="Yes",$S40="Yes",$X40="Yes",$AC40="Yes",$AH40="Yes"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="AN40" s="241">
+      <c r="AN41" s="241">
         <f>IF($A40="","",IFERROR(IF($AI40&lt;&gt;"",$AI40,IF($AD40&lt;&gt;"",$AD40,IF($Y40&lt;&gt;"",$Y40,IF($T40&lt;&gt;"",$T40,IF($O40&lt;&gt;"",$O40,""))))),""))</f>
         <v/>
       </c>
-      <c r="AO40" s="241">
+      <c r="AO41" s="241">
         <f>IFERROR(IF($AJ40&lt;&gt;"",$AJ40,IF($AE40&lt;&gt;"",$AE40,IF($Z40&lt;&gt;"",$Z40,IF($U40&lt;&gt;"",$U40,IF($P40&lt;&gt;"",$P40,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP40" s="240" t="inlineStr">
+      <c r="AP41" s="240" t="inlineStr">
         <is>
           <t>Technique: EP-delivered-blocked | Màn "Báo sự cố" (lối thoát thay thế) xác nhận Out of scope v1.0 — C-CNL-01 Resolved/Deferred → KHÔNG assert sự tồn tại màn này</t>
         </is>
       </c>
-    </row>
-    <row r="41" s="206">
-      <c r="A41" s="231" t="n"/>
-      <c r="B41" s="231" t="n"/>
-      <c r="C41" s="231" t="n"/>
-      <c r="D41" s="231" t="n"/>
-      <c r="E41" s="231" t="n"/>
-      <c r="F41" s="249" t="n"/>
-      <c r="G41" s="249" t="n"/>
-      <c r="H41" s="249" t="n"/>
-      <c r="I41" s="249" t="n"/>
-      <c r="J41" s="231" t="n"/>
-      <c r="K41" s="231" t="n"/>
-      <c r="L41" s="231" t="n"/>
-      <c r="M41" s="231" t="n"/>
-      <c r="N41" s="235" t="n"/>
-      <c r="O41" s="235" t="n"/>
-      <c r="P41" s="235" t="n"/>
-      <c r="Q41" s="235" t="n"/>
-      <c r="R41" s="235" t="n"/>
-      <c r="S41" s="235" t="n"/>
-      <c r="T41" s="235" t="n"/>
-      <c r="U41" s="235" t="n"/>
-      <c r="V41" s="235" t="n"/>
-      <c r="W41" s="235" t="n"/>
-      <c r="X41" s="235" t="n"/>
-      <c r="Y41" s="235" t="n"/>
-      <c r="Z41" s="235" t="n"/>
-      <c r="AA41" s="235" t="n"/>
-      <c r="AB41" s="236" t="n"/>
-      <c r="AC41" s="236" t="n"/>
-      <c r="AD41" s="236" t="n"/>
-      <c r="AE41" s="236" t="n"/>
-      <c r="AF41" s="236" t="n"/>
-      <c r="AG41" s="236" t="n"/>
-      <c r="AH41" s="236" t="n"/>
-      <c r="AI41" s="236" t="n"/>
-      <c r="AJ41" s="236" t="n"/>
-      <c r="AK41" s="236" t="n"/>
-      <c r="AL41" s="236" t="n"/>
-      <c r="AM41" s="237" t="n"/>
-      <c r="AN41" s="237" t="n"/>
-      <c r="AO41" s="237" t="n"/>
-      <c r="AP41" s="238" t="n"/>
     </row>
     <row r="42" s="206">
       <c r="A42" s="231" t="n"/>
@@ -20599,6 +20652,7 @@
     <mergeCell ref="AH5:AL5"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="B39:I39"/>
     <mergeCell ref="AC5:AG5"/>
     <mergeCell ref="J5:M5"/>
     <mergeCell ref="A3:B3"/>
@@ -20608,7 +20662,6 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D5:I5"/>
-    <mergeCell ref="B38:I38"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="X5:AB5"/>
     <mergeCell ref="B19:I19"/>
@@ -20619,7 +20672,7 @@
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="S5:W5"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="B36:I36"/>
   </mergeCells>
   <dataValidations count="8">
     <dataValidation sqref="J8:J17 J19:J502" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
@@ -20939,7 +20992,7 @@
         </is>
       </c>
       <c r="L4" s="253" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M4" s="254" t="inlineStr">
         <is>
@@ -21087,7 +21140,7 @@
     <row r="9">
       <c r="A9" s="205" t="inlineStr">
         <is>
-          <t>Total TCs derived: 27</t>
+          <t>Total TCs derived: 28</t>
         </is>
       </c>
     </row>
